--- a/src/Calculators.CashFlow.Tests/ExcelReader/Files/empty.xlsx
+++ b/src/Calculators.CashFlow.Tests/ExcelReader/Files/empty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\repos\PensionTools\src\Calculators.CashFlow.Tests\ExcelReader\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C501DB14-EB8B-46E5-8224-16D9ADEE9026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7FB9C3-3D1A-425C-845F-D8484EFCE967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="1305" windowWidth="32520" windowHeight="19200" tabRatio="598" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="870" yWindow="60" windowWidth="32520" windowHeight="19200" tabRatio="598" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Person" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -118,6 +118,15 @@
   </si>
   <si>
     <t>Steuerfluss</t>
+  </si>
+  <si>
+    <t>Nummer</t>
+  </si>
+  <si>
+    <t>Geschlecht</t>
+  </si>
+  <si>
+    <t>Geburtsdatum</t>
   </si>
 </sst>
 </file>
@@ -478,41 +487,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9246EE65-0125-4D81-8881-133F24534DB9}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="G1" s="6" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{50B90021-A4A0-45A1-A53D-DCC133D7E961}">
-      <formula1>"Alleinstehend, Verheiratet"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{736DE558-003D-4DA5-AF6A-2C1D3A15E6CD}">
-      <formula1>"Reformiert, Katholisch, Römisch-Katholisch, Andere"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/src/Calculators.CashFlow.Tests/ExcelReader/Files/empty.xlsx
+++ b/src/Calculators.CashFlow.Tests/ExcelReader/Files/empty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\repos\PensionTools\src\Calculators.CashFlow.Tests\ExcelReader\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7FB9C3-3D1A-425C-845F-D8484EFCE967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E9D259-4CD4-4D3D-A8EC-36A03CBD60E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="60" windowWidth="32520" windowHeight="19200" tabRatio="598" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20730" yWindow="135" windowWidth="19485" windowHeight="19200" tabRatio="598" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Person" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
   <si>
     <t>ID</t>
   </si>
@@ -60,21 +60,9 @@
     <t>Enddatum</t>
   </si>
   <si>
-    <t>Gemeindename</t>
-  </si>
-  <si>
-    <t>PLZ</t>
-  </si>
-  <si>
     <t>Kanton</t>
   </si>
   <si>
-    <t>ZH</t>
-  </si>
-  <si>
-    <t>Zürich</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -127,6 +115,12 @@
   </si>
   <si>
     <t>Geburtsdatum</t>
+  </si>
+  <si>
+    <t>Gemeinde Id</t>
+  </si>
+  <si>
+    <t>Steuer-Id</t>
   </si>
 </sst>
 </file>
@@ -499,25 +493,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -527,34 +521,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29DC190-0B98-4C71-BDF8-1792310B4F6D}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>5</v>
-      </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>8047</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -804,25 +786,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -898,25 +880,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>19</v>
-      </c>
       <c r="F1" s="6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -945,25 +927,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -994,25 +976,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
